--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.58548548234277</v>
+        <v>4.6451413908807</v>
       </c>
       <c r="D2" t="n">
-        <v>28.61535474376209</v>
+        <v>4.64999514586134</v>
       </c>
       <c r="E2" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F2" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80.13480956179136</v>
+        <v>13.0219065537911</v>
       </c>
       <c r="D3" t="n">
-        <v>79.64747637166752</v>
+        <v>12.94271491039597</v>
       </c>
       <c r="E3" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F3" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.00693776483858</v>
+        <v>2.926127386786269</v>
       </c>
       <c r="D4" t="n">
-        <v>17.46858205757364</v>
+        <v>2.838644584355716</v>
       </c>
       <c r="E4" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F4" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.57178135710812</v>
+        <v>3.667914470530069</v>
       </c>
       <c r="D5" t="n">
-        <v>30.59471848046147</v>
+        <v>4.971641753074989</v>
       </c>
       <c r="E5" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F5" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.577784974090244</v>
+        <v>1.393890058289665</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3496181520371</v>
+        <v>2.656812949706028</v>
       </c>
       <c r="E6" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F6" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.703188834919681</v>
+        <v>0.9267681856744482</v>
       </c>
       <c r="D7" t="n">
-        <v>1.310389324363528</v>
+        <v>0.2129382652090732</v>
       </c>
       <c r="E7" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F7" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.527473922932243</v>
+        <v>1.38571451247649</v>
       </c>
       <c r="D8" t="n">
-        <v>8.613420881892068</v>
+        <v>1.399680893307461</v>
       </c>
       <c r="E8" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F8" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.861101460093595</v>
+        <v>1.602428987265209</v>
       </c>
       <c r="D9" t="n">
-        <v>10.70928867782732</v>
+        <v>1.74025941014694</v>
       </c>
       <c r="E9" t="n">
-        <v>22.93863264287885</v>
+        <v>3.727527804467814</v>
       </c>
       <c r="F9" t="n">
-        <v>22.88726535092289</v>
+        <v>3.71918061952497</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
